--- a/costpulse/tests/data/synthetic_messy.xlsx
+++ b/costpulse/tests/data/synthetic_messy.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1524,32 +1524,452 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>P-1013</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>Shaft machined</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Machining</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Beta Machining</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>220000</v>
+      </c>
+      <c r="G19" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="H19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>EUR 0.18</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="P19" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>500</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>42CrMo4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>P-1014</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Flange machined</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Machining</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Theta CNC</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>130000</v>
+      </c>
+      <c r="G20" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="H20" t="n">
+        <v>16</v>
+      </c>
+      <c r="I20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>EUR 0.24</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="P20" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1200</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>AlSi9Cu3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>P-1015</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Hub machined</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Machining</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Beta Machining</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>110000</v>
+      </c>
+      <c r="G21" t="n">
+        <v>19</v>
+      </c>
+      <c r="H21" t="n">
+        <v>18</v>
+      </c>
+      <c r="I21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>EUR 0.28</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="P21" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1600</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>20MnCr5</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>P-1016</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Carrier machined</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Machining</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Theta CNC</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>95000</v>
+      </c>
+      <c r="G22" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="H22" t="n">
+        <v>24</v>
+      </c>
+      <c r="I22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>EUR 0.42</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="P22" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2800</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>AlSi9Cu3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>P-1017</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Diff case machined</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Machining</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Beta Machining</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>80000</v>
+      </c>
+      <c r="G23" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="I23" t="n">
+        <v>11</v>
+      </c>
+      <c r="J23" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>EUR 0.50</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="P23" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3500</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>GJS-600</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>P-1018</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Valve body machined</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Machining</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Iota Precision</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>140000</v>
+      </c>
+      <c r="G24" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="H24" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="I24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J24" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="L24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>EUR 0.30</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="P24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>AlSi9Cu3</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="n">
-        <v>245.15</v>
-      </c>
-      <c r="H19" t="n">
-        <v>223.38</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>371.25</v>
+      </c>
+      <c r="H25" t="n">
+        <v>342.58</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
